--- a/edim-ai-blueprint/docs/EDIM_DB정의서.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_DB정의서.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1189개</t>
+          <t>1190개</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>3</v>
@@ -3762,7 +3762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1190"/>
+  <dimension ref="A1:H1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -36536,32 +36536,28 @@
     <row r="1047">
       <c r="A1047" s="2" t="inlineStr">
         <is>
-          <t>sys_user_pref</t>
+          <t>sys_user</t>
         </is>
       </c>
       <c r="B1047" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C1047" s="2" t="inlineStr">
         <is>
-          <t>pref_id</t>
+          <t>pw_changed_at</t>
         </is>
       </c>
       <c r="D1047" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1047" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1047" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1047" s="2" t="inlineStr"/>
       <c r="G1047" s="2" t="inlineStr"/>
       <c r="H1047" s="2" t="inlineStr"/>
     </row>
@@ -36572,11 +36568,11 @@
         </is>
       </c>
       <c r="B1048" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1048" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>pref_id</t>
         </is>
       </c>
       <c r="D1048" s="2" t="inlineStr">
@@ -36591,7 +36587,7 @@
       </c>
       <c r="F1048" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G1048" s="2" t="inlineStr"/>
@@ -36604,16 +36600,16 @@
         </is>
       </c>
       <c r="B1049" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1049" s="2" t="inlineStr">
         <is>
-          <t>login_id</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1049" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1049" s="2" t="inlineStr">
@@ -36636,16 +36632,16 @@
         </is>
       </c>
       <c r="B1050" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1050" s="2" t="inlineStr">
         <is>
-          <t>pref_key</t>
+          <t>login_id</t>
         </is>
       </c>
       <c r="D1050" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(60)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1050" s="2" t="inlineStr">
@@ -36668,16 +36664,16 @@
         </is>
       </c>
       <c r="B1051" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1051" s="2" t="inlineStr">
         <is>
-          <t>pref_value</t>
+          <t>pref_key</t>
         </is>
       </c>
       <c r="D1051" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(60)</t>
         </is>
       </c>
       <c r="E1051" s="2" t="inlineStr">
@@ -36685,12 +36681,12 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1051" s="2" t="inlineStr"/>
-      <c r="G1051" s="2" t="inlineStr">
-        <is>
-          <t>'{}'::jsonb</t>
-        </is>
-      </c>
+      <c r="F1051" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="G1051" s="2" t="inlineStr"/>
       <c r="H1051" s="2" t="inlineStr"/>
     </row>
     <row r="1052">
@@ -36700,16 +36696,16 @@
         </is>
       </c>
       <c r="B1052" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1052" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>pref_value</t>
         </is>
       </c>
       <c r="D1052" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1052" s="2" t="inlineStr">
@@ -36720,7 +36716,7 @@
       <c r="F1052" s="2" t="inlineStr"/>
       <c r="G1052" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'{}'::jsonb</t>
         </is>
       </c>
       <c r="H1052" s="2" t="inlineStr"/>
@@ -36728,20 +36724,20 @@
     <row r="1053">
       <c r="A1053" s="2" t="inlineStr">
         <is>
-          <t>sys_user_role</t>
+          <t>sys_user_pref</t>
         </is>
       </c>
       <c r="B1053" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1053" s="2" t="inlineStr">
         <is>
-          <t>user_role_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1053" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1053" s="2" t="inlineStr">
@@ -36749,12 +36745,12 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1053" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1053" s="2" t="inlineStr"/>
+      <c r="F1053" s="2" t="inlineStr"/>
+      <c r="G1053" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1053" s="2" t="inlineStr"/>
     </row>
     <row r="1054">
@@ -36764,11 +36760,11 @@
         </is>
       </c>
       <c r="B1054" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>user_role_id</t>
         </is>
       </c>
       <c r="D1054" s="2" t="inlineStr">
@@ -36783,7 +36779,7 @@
       </c>
       <c r="F1054" s="2" t="inlineStr">
         <is>
-          <t>FK→sys_user · UQ</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G1054" s="2" t="inlineStr"/>
@@ -36796,11 +36792,11 @@
         </is>
       </c>
       <c r="B1055" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1055" s="2" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D1055" s="2" t="inlineStr">
@@ -36815,7 +36811,7 @@
       </c>
       <c r="F1055" s="2" t="inlineStr">
         <is>
-          <t>FK→sys_role · UQ</t>
+          <t>FK→sys_user · UQ</t>
         </is>
       </c>
       <c r="G1055" s="2" t="inlineStr"/>
@@ -36824,15 +36820,15 @@
     <row r="1056">
       <c r="A1056" s="2" t="inlineStr">
         <is>
-          <t>sys_work_lock</t>
+          <t>sys_user_role</t>
         </is>
       </c>
       <c r="B1056" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>lock_id</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr">
@@ -36847,14 +36843,10 @@
       </c>
       <c r="F1056" s="2" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1056" s="2" t="inlineStr">
-        <is>
-          <t>nextval('sys_work_lock_lock_id_seq'::regclass)</t>
-        </is>
-      </c>
+          <t>FK→sys_role · UQ</t>
+        </is>
+      </c>
+      <c r="G1056" s="2" t="inlineStr"/>
       <c r="H1056" s="2" t="inlineStr"/>
     </row>
     <row r="1057">
@@ -36864,11 +36856,11 @@
         </is>
       </c>
       <c r="B1057" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1057" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>lock_id</t>
         </is>
       </c>
       <c r="D1057" s="2" t="inlineStr">
@@ -36881,8 +36873,16 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1057" s="2" t="inlineStr"/>
-      <c r="G1057" s="2" t="inlineStr"/>
+      <c r="F1057" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G1057" s="2" t="inlineStr">
+        <is>
+          <t>nextval('sys_work_lock_lock_id_seq'::regclass)</t>
+        </is>
+      </c>
       <c r="H1057" s="2" t="inlineStr"/>
     </row>
     <row r="1058">
@@ -36892,16 +36892,16 @@
         </is>
       </c>
       <c r="B1058" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>resource_kind</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1058" s="2" t="inlineStr">
@@ -36920,16 +36920,16 @@
         </is>
       </c>
       <c r="B1059" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1059" s="2" t="inlineStr">
         <is>
-          <t>resource_key</t>
+          <t>resource_kind</t>
         </is>
       </c>
       <c r="D1059" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1059" s="2" t="inlineStr">
@@ -36948,16 +36948,16 @@
         </is>
       </c>
       <c r="B1060" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>holder_id</t>
+          <t>resource_key</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="E1060" s="2" t="inlineStr">
@@ -36976,16 +36976,16 @@
         </is>
       </c>
       <c r="B1061" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1061" s="2" t="inlineStr">
         <is>
-          <t>acquired_at</t>
+          <t>holder_id</t>
         </is>
       </c>
       <c r="D1061" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1061" s="2" t="inlineStr">
@@ -36994,11 +36994,7 @@
         </is>
       </c>
       <c r="F1061" s="2" t="inlineStr"/>
-      <c r="G1061" s="2" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="G1061" s="2" t="inlineStr"/>
       <c r="H1061" s="2" t="inlineStr"/>
     </row>
     <row r="1062">
@@ -37008,11 +37004,11 @@
         </is>
       </c>
       <c r="B1062" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr">
@@ -37026,7 +37022,11 @@
         </is>
       </c>
       <c r="F1062" s="2" t="inlineStr"/>
-      <c r="G1062" s="2" t="inlineStr"/>
+      <c r="G1062" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1062" s="2" t="inlineStr"/>
     </row>
     <row r="1063">
@@ -37036,21 +37036,21 @@
         </is>
       </c>
       <c r="B1063" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1063" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="D1063" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1063" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1063" s="2" t="inlineStr"/>
@@ -37060,32 +37060,28 @@
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
         <is>
-          <t>tax_code</t>
+          <t>sys_work_lock</t>
         </is>
       </c>
       <c r="B1064" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>tax_id</t>
+          <t>note</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="E1064" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1064" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1064" s="2" t="inlineStr"/>
       <c r="G1064" s="2" t="inlineStr"/>
       <c r="H1064" s="2" t="inlineStr"/>
     </row>
@@ -37096,11 +37092,11 @@
         </is>
       </c>
       <c r="B1065" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1065" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>tax_id</t>
         </is>
       </c>
       <c r="D1065" s="2" t="inlineStr">
@@ -37115,7 +37111,7 @@
       </c>
       <c r="F1065" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G1065" s="2" t="inlineStr"/>
@@ -37128,16 +37124,16 @@
         </is>
       </c>
       <c r="B1066" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1066" s="2" t="inlineStr">
@@ -37160,16 +37156,16 @@
         </is>
       </c>
       <c r="B1067" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1067" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>code</t>
         </is>
       </c>
       <c r="D1067" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1067" s="2" t="inlineStr">
@@ -37177,7 +37173,11 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1067" s="2" t="inlineStr"/>
+      <c r="F1067" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G1067" s="2" t="inlineStr"/>
       <c r="H1067" s="2" t="inlineStr"/>
     </row>
@@ -37188,16 +37188,16 @@
         </is>
       </c>
       <c r="B1068" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>rate_pct</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D1068" s="2" t="inlineStr">
         <is>
-          <t>NUMERIC(5,2)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E1068" s="2" t="inlineStr">
@@ -37206,11 +37206,7 @@
         </is>
       </c>
       <c r="F1068" s="2" t="inlineStr"/>
-      <c r="G1068" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="G1068" s="2" t="inlineStr"/>
       <c r="H1068" s="2" t="inlineStr"/>
     </row>
     <row r="1069">
@@ -37220,16 +37216,16 @@
         </is>
       </c>
       <c r="B1069" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1069" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>rate_pct</t>
         </is>
       </c>
       <c r="D1069" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>NUMERIC(5,2)</t>
         </is>
       </c>
       <c r="E1069" s="2" t="inlineStr">
@@ -37240,7 +37236,7 @@
       <c r="F1069" s="2" t="inlineStr"/>
       <c r="G1069" s="2" t="inlineStr">
         <is>
-          <t>'system'::character varying</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H1069" s="2" t="inlineStr"/>
@@ -37248,20 +37244,20 @@
     <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
         <is>
-          <t>tbl_data_row</t>
+          <t>tax_code</t>
         </is>
       </c>
       <c r="B1070" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>row_id</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1070" s="2" t="inlineStr">
@@ -37269,12 +37265,12 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1070" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1070" s="2" t="inlineStr"/>
+      <c r="F1070" s="2" t="inlineStr"/>
+      <c r="G1070" s="2" t="inlineStr">
+        <is>
+          <t>'system'::character varying</t>
+        </is>
+      </c>
       <c r="H1070" s="2" t="inlineStr"/>
     </row>
     <row r="1071">
@@ -37284,11 +37280,11 @@
         </is>
       </c>
       <c r="B1071" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1071" s="2" t="inlineStr">
         <is>
-          <t>table_id</t>
+          <t>row_id</t>
         </is>
       </c>
       <c r="D1071" s="2" t="inlineStr">
@@ -37303,7 +37299,7 @@
       </c>
       <c r="F1071" s="2" t="inlineStr">
         <is>
-          <t>FK→tbl_data_table · UQ</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G1071" s="2" t="inlineStr"/>
@@ -37316,16 +37312,16 @@
         </is>
       </c>
       <c r="B1072" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>row_key</t>
+          <t>table_id</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1072" s="2" t="inlineStr">
@@ -37335,15 +37331,11 @@
       </c>
       <c r="F1072" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>FK→tbl_data_table · UQ</t>
         </is>
       </c>
       <c r="G1072" s="2" t="inlineStr"/>
-      <c r="H1072" s="2" t="inlineStr">
-        <is>
-          <t>Key 열 값 (Size: 560, 630…)</t>
-        </is>
-      </c>
+      <c r="H1072" s="2" t="inlineStr"/>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
@@ -37352,28 +37344,32 @@
         </is>
       </c>
       <c r="B1073" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1073" s="2" t="inlineStr">
         <is>
-          <t>row_key_num</t>
+          <t>row_key</t>
         </is>
       </c>
       <c r="D1073" s="2" t="inlineStr">
         <is>
-          <t>NUMERIC(18,4)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1073" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1073" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1073" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G1073" s="2" t="inlineStr"/>
       <c r="H1073" s="2" t="inlineStr">
         <is>
-          <t>row_key 숫자 해석값 — Macro 범위 조회(10:25) 정렬용, 저장 시 파싱 (v0.3 결함 수정: VARCHAR 사전순은 "1000" &lt; "560")</t>
+          <t>Key 열 값 (Size: 560, 630…)</t>
         </is>
       </c>
     </row>
@@ -37384,28 +37380,28 @@
         </is>
       </c>
       <c r="B1074" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>row_values</t>
+          <t>row_key_num</t>
         </is>
       </c>
       <c r="D1074" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>NUMERIC(18,4)</t>
         </is>
       </c>
       <c r="E1074" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1074" s="2" t="inlineStr"/>
       <c r="G1074" s="2" t="inlineStr"/>
       <c r="H1074" s="2" t="inlineStr">
         <is>
-          <t>{"A":55,"B":45,...,"Remarks":"656"}</t>
+          <t>row_key 숫자 해석값 — Macro 범위 조회(10:25) 정렬용, 저장 시 파싱 (v0.3 결함 수정: VARCHAR 사전순은 "1000" &lt; "560")</t>
         </is>
       </c>
     </row>
@@ -37416,16 +37412,16 @@
         </is>
       </c>
       <c r="B1075" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1075" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>row_values</t>
         </is>
       </c>
       <c r="D1075" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1075" s="2" t="inlineStr">
@@ -37434,30 +37430,30 @@
         </is>
       </c>
       <c r="F1075" s="2" t="inlineStr"/>
-      <c r="G1075" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H1075" s="2" t="inlineStr"/>
+      <c r="G1075" s="2" t="inlineStr"/>
+      <c r="H1075" s="2" t="inlineStr">
+        <is>
+          <t>{"A":55,"B":45,...,"Remarks":"656"}</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>tbl_data_row</t>
         </is>
       </c>
       <c r="B1076" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>table_id</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="D1076" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="E1076" s="2" t="inlineStr">
@@ -37465,12 +37461,12 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1076" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1076" s="2" t="inlineStr"/>
+      <c r="F1076" s="2" t="inlineStr"/>
+      <c r="G1076" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H1076" s="2" t="inlineStr"/>
     </row>
     <row r="1077">
@@ -37480,11 +37476,11 @@
         </is>
       </c>
       <c r="B1077" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1077" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>table_id</t>
         </is>
       </c>
       <c r="D1077" s="2" t="inlineStr">
@@ -37499,7 +37495,7 @@
       </c>
       <c r="F1077" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G1077" s="2" t="inlineStr"/>
@@ -37512,16 +37508,16 @@
         </is>
       </c>
       <c r="B1078" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>table_name</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1078" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1078" s="2" t="inlineStr">
@@ -37535,11 +37531,7 @@
         </is>
       </c>
       <c r="G1078" s="2" t="inlineStr"/>
-      <c r="H1078" s="2" t="inlineStr">
-        <is>
-          <t>Macro 참조명</t>
-        </is>
-      </c>
+      <c r="H1078" s="2" t="inlineStr"/>
     </row>
     <row r="1079">
       <c r="A1079" s="2" t="inlineStr">
@@ -37548,16 +37540,16 @@
         </is>
       </c>
       <c r="B1079" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1079" s="2" t="inlineStr">
         <is>
-          <t>table_type</t>
+          <t>table_name</t>
         </is>
       </c>
       <c r="D1079" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E1079" s="2" t="inlineStr">
@@ -37567,13 +37559,13 @@
       </c>
       <c r="F1079" s="2" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G1079" s="2" t="inlineStr"/>
       <c r="H1079" s="2" t="inlineStr">
         <is>
-          <t>VARIANT / TECH / MATERIAL / STD / GENERATED</t>
+          <t>Macro 참조명</t>
         </is>
       </c>
     </row>
@@ -37584,28 +37576,32 @@
         </is>
       </c>
       <c r="B1080" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>table_type</t>
         </is>
       </c>
       <c r="D1080" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1080" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1080" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1080" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
       <c r="G1080" s="2" t="inlineStr"/>
       <c r="H1080" s="2" t="inlineStr">
         <is>
-          <t>관리 부서 (Engineering 등)</t>
+          <t>VARIANT / TECH / MATERIAL / STD / GENERATED</t>
         </is>
       </c>
     </row>
@@ -37616,28 +37612,28 @@
         </is>
       </c>
       <c r="B1081" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1081" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_address</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D1081" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1081" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1081" s="2" t="inlineStr"/>
       <c r="G1081" s="2" t="inlineStr"/>
       <c r="H1081" s="2" t="inlineStr">
         <is>
-          <t>Table Address (Hierarchy 주소)</t>
+          <t>관리 부서 (Engineering 등)</t>
         </is>
       </c>
     </row>
@@ -37648,16 +37644,16 @@
         </is>
       </c>
       <c r="B1082" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>column_def</t>
+          <t>hierarchy_address</t>
         </is>
       </c>
       <c r="D1082" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E1082" s="2" t="inlineStr">
@@ -37669,7 +37665,7 @@
       <c r="G1082" s="2" t="inlineStr"/>
       <c r="H1082" s="2" t="inlineStr">
         <is>
-          <t>열 정의: Key No, A~N, 타입, 단위</t>
+          <t>Table Address (Hierarchy 주소)</t>
         </is>
       </c>
     </row>
@@ -37680,26 +37676,30 @@
         </is>
       </c>
       <c r="B1083" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1083" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_def</t>
         </is>
       </c>
       <c r="D1083" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1083" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1083" s="2" t="inlineStr"/>
       <c r="G1083" s="2" t="inlineStr"/>
-      <c r="H1083" s="2" t="inlineStr"/>
+      <c r="H1083" s="2" t="inlineStr">
+        <is>
+          <t>열 정의: Key No, A~N, 타입, 단위</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
@@ -37708,34 +37708,26 @@
         </is>
       </c>
       <c r="B1084" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>approval_status</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D1084" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E1084" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1084" s="2" t="inlineStr"/>
-      <c r="G1084" s="2" t="inlineStr">
-        <is>
-          <t>'DRAFT'::character varying</t>
-        </is>
-      </c>
-      <c r="H1084" s="2" t="inlineStr">
-        <is>
-          <t>DB로서의 명확한 구성 요구 (E-4)</t>
-        </is>
-      </c>
+      <c r="G1084" s="2" t="inlineStr"/>
+      <c r="H1084" s="2" t="inlineStr"/>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
@@ -37744,16 +37736,16 @@
         </is>
       </c>
       <c r="B1085" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1085" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="D1085" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1085" s="2" t="inlineStr">
@@ -37764,10 +37756,14 @@
       <c r="F1085" s="2" t="inlineStr"/>
       <c r="G1085" s="2" t="inlineStr">
         <is>
-          <t>'system'::character varying</t>
-        </is>
-      </c>
-      <c r="H1085" s="2" t="inlineStr"/>
+          <t>'DRAFT'::character varying</t>
+        </is>
+      </c>
+      <c r="H1085" s="2" t="inlineStr">
+        <is>
+          <t>DB로서의 명확한 구성 요구 (E-4)</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
@@ -37776,16 +37772,16 @@
         </is>
       </c>
       <c r="B1086" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1086" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1086" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1086" s="2" t="inlineStr">
@@ -37796,7 +37792,7 @@
       <c r="F1086" s="2" t="inlineStr"/>
       <c r="G1086" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'system'::character varying</t>
         </is>
       </c>
       <c r="H1086" s="2" t="inlineStr"/>
@@ -37808,25 +37804,29 @@
         </is>
       </c>
       <c r="B1087" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1087" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1087" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1087" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1087" s="2" t="inlineStr"/>
-      <c r="G1087" s="2" t="inlineStr"/>
+      <c r="G1087" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1087" s="2" t="inlineStr"/>
     </row>
     <row r="1088">
@@ -37836,16 +37836,16 @@
         </is>
       </c>
       <c r="B1088" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1088" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D1088" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1088" s="2" t="inlineStr">
@@ -37860,37 +37860,29 @@
     <row r="1089">
       <c r="A1089" s="2" t="inlineStr">
         <is>
-          <t>tbx_binding_contract</t>
+          <t>tbl_data_table</t>
         </is>
       </c>
       <c r="B1089" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1089" s="2" t="inlineStr">
         <is>
-          <t>contract_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1089" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1089" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1089" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1089" s="2" t="inlineStr">
-        <is>
-          <t>nextval('tbx_binding_contract_contract_id_seq'::regclass)</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1089" s="2" t="inlineStr"/>
+      <c r="G1089" s="2" t="inlineStr"/>
       <c r="H1089" s="2" t="inlineStr"/>
     </row>
     <row r="1090">
@@ -37900,11 +37892,11 @@
         </is>
       </c>
       <c r="B1090" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1090" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>contract_id</t>
         </is>
       </c>
       <c r="D1090" s="2" t="inlineStr">
@@ -37919,10 +37911,14 @@
       </c>
       <c r="F1090" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G1090" s="2" t="inlineStr"/>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G1090" s="2" t="inlineStr">
+        <is>
+          <t>nextval('tbx_binding_contract_contract_id_seq'::regclass)</t>
+        </is>
+      </c>
       <c r="H1090" s="2" t="inlineStr"/>
     </row>
     <row r="1091">
@@ -37932,16 +37928,16 @@
         </is>
       </c>
       <c r="B1091" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1091" s="2" t="inlineStr">
         <is>
-          <t>contract_code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1091" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(40)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1091" s="2" t="inlineStr">
@@ -37964,16 +37960,16 @@
         </is>
       </c>
       <c r="B1092" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1092" s="2" t="inlineStr">
         <is>
-          <t>contract_name</t>
+          <t>contract_code</t>
         </is>
       </c>
       <c r="D1092" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="E1092" s="2" t="inlineStr">
@@ -37981,7 +37977,11 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1092" s="2" t="inlineStr"/>
+      <c r="F1092" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G1092" s="2" t="inlineStr"/>
       <c r="H1092" s="2" t="inlineStr"/>
     </row>
@@ -37992,16 +37992,16 @@
         </is>
       </c>
       <c r="B1093" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1093" s="2" t="inlineStr">
         <is>
-          <t>source_kind</t>
+          <t>contract_name</t>
         </is>
       </c>
       <c r="D1093" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="E1093" s="2" t="inlineStr">
@@ -38009,16 +38009,8 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1093" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="G1093" s="2" t="inlineStr">
-        <is>
-          <t>'TABLE'::character varying</t>
-        </is>
-      </c>
+      <c r="F1093" s="2" t="inlineStr"/>
+      <c r="G1093" s="2" t="inlineStr"/>
       <c r="H1093" s="2" t="inlineStr"/>
     </row>
     <row r="1094">
@@ -38028,16 +38020,16 @@
         </is>
       </c>
       <c r="B1094" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1094" s="2" t="inlineStr">
         <is>
-          <t>source_ref</t>
+          <t>source_kind</t>
         </is>
       </c>
       <c r="D1094" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E1094" s="2" t="inlineStr">
@@ -38045,8 +38037,16 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1094" s="2" t="inlineStr"/>
-      <c r="G1094" s="2" t="inlineStr"/>
+      <c r="F1094" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G1094" s="2" t="inlineStr">
+        <is>
+          <t>'TABLE'::character varying</t>
+        </is>
+      </c>
       <c r="H1094" s="2" t="inlineStr"/>
     </row>
     <row r="1095">
@@ -38056,16 +38056,16 @@
         </is>
       </c>
       <c r="B1095" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1095" s="2" t="inlineStr">
         <is>
-          <t>allowed_fields</t>
+          <t>source_ref</t>
         </is>
       </c>
       <c r="D1095" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="E1095" s="2" t="inlineStr">
@@ -38074,11 +38074,7 @@
         </is>
       </c>
       <c r="F1095" s="2" t="inlineStr"/>
-      <c r="G1095" s="2" t="inlineStr">
-        <is>
-          <t>'[]'::jsonb</t>
-        </is>
-      </c>
+      <c r="G1095" s="2" t="inlineStr"/>
       <c r="H1095" s="2" t="inlineStr"/>
     </row>
     <row r="1096">
@@ -38088,16 +38084,16 @@
         </is>
       </c>
       <c r="B1096" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1096" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>allowed_fields</t>
         </is>
       </c>
       <c r="D1096" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(12)</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1096" s="2" t="inlineStr">
@@ -38105,14 +38101,10 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1096" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
+      <c r="F1096" s="2" t="inlineStr"/>
       <c r="G1096" s="2" t="inlineStr">
         <is>
-          <t>'DRAFT'::character varying</t>
+          <t>'[]'::jsonb</t>
         </is>
       </c>
       <c r="H1096" s="2" t="inlineStr"/>
@@ -38124,25 +38116,33 @@
         </is>
       </c>
       <c r="B1097" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1097" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D1097" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(300)</t>
+          <t>VARCHAR(12)</t>
         </is>
       </c>
       <c r="E1097" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1097" s="2" t="inlineStr"/>
-      <c r="G1097" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1097" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G1097" s="2" t="inlineStr">
+        <is>
+          <t>'DRAFT'::character varying</t>
+        </is>
+      </c>
       <c r="H1097" s="2" t="inlineStr"/>
     </row>
     <row r="1098">
@@ -38152,29 +38152,25 @@
         </is>
       </c>
       <c r="B1098" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1098" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>note</t>
         </is>
       </c>
       <c r="D1098" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(300)</t>
         </is>
       </c>
       <c r="E1098" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1098" s="2" t="inlineStr"/>
-      <c r="G1098" s="2" t="inlineStr">
-        <is>
-          <t>'system'::character varying</t>
-        </is>
-      </c>
+      <c r="G1098" s="2" t="inlineStr"/>
       <c r="H1098" s="2" t="inlineStr"/>
     </row>
     <row r="1099">
@@ -38184,16 +38180,16 @@
         </is>
       </c>
       <c r="B1099" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1099" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1099" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1099" s="2" t="inlineStr">
@@ -38204,7 +38200,7 @@
       <c r="F1099" s="2" t="inlineStr"/>
       <c r="G1099" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'system'::character varying</t>
         </is>
       </c>
       <c r="H1099" s="2" t="inlineStr"/>
@@ -38216,25 +38212,29 @@
         </is>
       </c>
       <c r="B1100" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1100" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1100" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1100" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1100" s="2" t="inlineStr"/>
-      <c r="G1100" s="2" t="inlineStr"/>
+      <c r="G1100" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1100" s="2" t="inlineStr"/>
     </row>
     <row r="1101">
@@ -38244,16 +38244,16 @@
         </is>
       </c>
       <c r="B1101" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1101" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D1101" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1101" s="2" t="inlineStr">
@@ -38268,37 +38268,29 @@
     <row r="1102">
       <c r="A1102" s="2" t="inlineStr">
         <is>
-          <t>tbx_command</t>
+          <t>tbx_binding_contract</t>
         </is>
       </c>
       <c r="B1102" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1102" s="2" t="inlineStr">
         <is>
-          <t>command_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1102" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1102" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1102" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1102" s="2" t="inlineStr">
-        <is>
-          <t>nextval('tbx_command_command_id_seq'::regclass)</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1102" s="2" t="inlineStr"/>
+      <c r="G1102" s="2" t="inlineStr"/>
       <c r="H1102" s="2" t="inlineStr"/>
     </row>
     <row r="1103">
@@ -38308,11 +38300,11 @@
         </is>
       </c>
       <c r="B1103" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1103" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>command_id</t>
         </is>
       </c>
       <c r="D1103" s="2" t="inlineStr">
@@ -38327,10 +38319,14 @@
       </c>
       <c r="F1103" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G1103" s="2" t="inlineStr"/>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G1103" s="2" t="inlineStr">
+        <is>
+          <t>nextval('tbx_command_command_id_seq'::regclass)</t>
+        </is>
+      </c>
       <c r="H1103" s="2" t="inlineStr"/>
     </row>
     <row r="1104">
@@ -38340,16 +38336,16 @@
         </is>
       </c>
       <c r="B1104" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1104" s="2" t="inlineStr">
         <is>
-          <t>command_code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1104" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(40)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1104" s="2" t="inlineStr">
@@ -38372,16 +38368,16 @@
         </is>
       </c>
       <c r="B1105" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1105" s="2" t="inlineStr">
         <is>
-          <t>command_name</t>
+          <t>command_code</t>
         </is>
       </c>
       <c r="D1105" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="E1105" s="2" t="inlineStr">
@@ -38389,7 +38385,11 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1105" s="2" t="inlineStr"/>
+      <c r="F1105" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G1105" s="2" t="inlineStr"/>
       <c r="H1105" s="2" t="inlineStr"/>
     </row>
@@ -38400,16 +38400,16 @@
         </is>
       </c>
       <c r="B1106" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1106" s="2" t="inlineStr">
         <is>
-          <t>handler_kind</t>
+          <t>command_name</t>
         </is>
       </c>
       <c r="D1106" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="E1106" s="2" t="inlineStr">
@@ -38417,16 +38417,8 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1106" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="G1106" s="2" t="inlineStr">
-        <is>
-          <t>'MACRO'::character varying</t>
-        </is>
-      </c>
+      <c r="F1106" s="2" t="inlineStr"/>
+      <c r="G1106" s="2" t="inlineStr"/>
       <c r="H1106" s="2" t="inlineStr"/>
     </row>
     <row r="1107">
@@ -38436,16 +38428,16 @@
         </is>
       </c>
       <c r="B1107" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1107" s="2" t="inlineStr">
         <is>
-          <t>handler_ref</t>
+          <t>handler_kind</t>
         </is>
       </c>
       <c r="D1107" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E1107" s="2" t="inlineStr">
@@ -38453,8 +38445,16 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1107" s="2" t="inlineStr"/>
-      <c r="G1107" s="2" t="inlineStr"/>
+      <c r="F1107" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G1107" s="2" t="inlineStr">
+        <is>
+          <t>'MACRO'::character varying</t>
+        </is>
+      </c>
       <c r="H1107" s="2" t="inlineStr"/>
     </row>
     <row r="1108">
@@ -38464,16 +38464,16 @@
         </is>
       </c>
       <c r="B1108" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1108" s="2" t="inlineStr">
         <is>
-          <t>required_context</t>
+          <t>handler_ref</t>
         </is>
       </c>
       <c r="D1108" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="E1108" s="2" t="inlineStr">
@@ -38482,11 +38482,7 @@
         </is>
       </c>
       <c r="F1108" s="2" t="inlineStr"/>
-      <c r="G1108" s="2" t="inlineStr">
-        <is>
-          <t>'[]'::jsonb</t>
-        </is>
-      </c>
+      <c r="G1108" s="2" t="inlineStr"/>
       <c r="H1108" s="2" t="inlineStr"/>
     </row>
     <row r="1109">
@@ -38496,16 +38492,16 @@
         </is>
       </c>
       <c r="B1109" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1109" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>required_context</t>
         </is>
       </c>
       <c r="D1109" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(12)</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1109" s="2" t="inlineStr">
@@ -38513,14 +38509,10 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1109" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
+      <c r="F1109" s="2" t="inlineStr"/>
       <c r="G1109" s="2" t="inlineStr">
         <is>
-          <t>'DRAFT'::character varying</t>
+          <t>'[]'::jsonb</t>
         </is>
       </c>
       <c r="H1109" s="2" t="inlineStr"/>
@@ -38532,25 +38524,33 @@
         </is>
       </c>
       <c r="B1110" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1110" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D1110" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(300)</t>
+          <t>VARCHAR(12)</t>
         </is>
       </c>
       <c r="E1110" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1110" s="2" t="inlineStr"/>
-      <c r="G1110" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1110" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G1110" s="2" t="inlineStr">
+        <is>
+          <t>'DRAFT'::character varying</t>
+        </is>
+      </c>
       <c r="H1110" s="2" t="inlineStr"/>
     </row>
     <row r="1111">
@@ -38560,29 +38560,25 @@
         </is>
       </c>
       <c r="B1111" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1111" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>note</t>
         </is>
       </c>
       <c r="D1111" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(300)</t>
         </is>
       </c>
       <c r="E1111" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1111" s="2" t="inlineStr"/>
-      <c r="G1111" s="2" t="inlineStr">
-        <is>
-          <t>'system'::character varying</t>
-        </is>
-      </c>
+      <c r="G1111" s="2" t="inlineStr"/>
       <c r="H1111" s="2" t="inlineStr"/>
     </row>
     <row r="1112">
@@ -38592,16 +38588,16 @@
         </is>
       </c>
       <c r="B1112" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1112" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1112" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1112" s="2" t="inlineStr">
@@ -38612,7 +38608,7 @@
       <c r="F1112" s="2" t="inlineStr"/>
       <c r="G1112" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'system'::character varying</t>
         </is>
       </c>
       <c r="H1112" s="2" t="inlineStr"/>
@@ -38624,25 +38620,29 @@
         </is>
       </c>
       <c r="B1113" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1113" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1113" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1113" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1113" s="2" t="inlineStr"/>
-      <c r="G1113" s="2" t="inlineStr"/>
+      <c r="G1113" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1113" s="2" t="inlineStr"/>
     </row>
     <row r="1114">
@@ -38652,16 +38652,16 @@
         </is>
       </c>
       <c r="B1114" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1114" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D1114" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1114" s="2" t="inlineStr">
@@ -38676,32 +38676,28 @@
     <row r="1115">
       <c r="A1115" s="2" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>tbx_command</t>
         </is>
       </c>
       <c r="B1115" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1115" s="2" t="inlineStr">
         <is>
-          <t>macro_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1115" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1115" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1115" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1115" s="2" t="inlineStr"/>
       <c r="G1115" s="2" t="inlineStr"/>
       <c r="H1115" s="2" t="inlineStr"/>
     </row>
@@ -38712,11 +38708,11 @@
         </is>
       </c>
       <c r="B1116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1116" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>macro_id</t>
         </is>
       </c>
       <c r="D1116" s="2" t="inlineStr">
@@ -38731,7 +38727,7 @@
       </c>
       <c r="F1116" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G1116" s="2" t="inlineStr"/>
@@ -38744,16 +38740,16 @@
         </is>
       </c>
       <c r="B1117" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1117" s="2" t="inlineStr">
         <is>
-          <t>macro_name</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1117" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1117" s="2" t="inlineStr">
@@ -38776,16 +38772,16 @@
         </is>
       </c>
       <c r="B1118" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1118" s="2" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>macro_name</t>
         </is>
       </c>
       <c r="D1118" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E1118" s="2" t="inlineStr">
@@ -38798,16 +38794,8 @@
           <t>UQ</t>
         </is>
       </c>
-      <c r="G1118" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H1118" s="2" t="inlineStr">
-        <is>
-          <t>UQ(tenant_id, macro_name, version)</t>
-        </is>
-      </c>
+      <c r="G1118" s="2" t="inlineStr"/>
+      <c r="H1118" s="2" t="inlineStr"/>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="inlineStr">
@@ -38816,28 +38804,36 @@
         </is>
       </c>
       <c r="B1119" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1119" s="2" t="inlineStr">
         <is>
-          <t>prompt_text</t>
+          <t>version</t>
         </is>
       </c>
       <c r="D1119" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="E1119" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1119" s="2" t="inlineStr"/>
-      <c r="G1119" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1119" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
+      <c r="G1119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H1119" s="2" t="inlineStr">
         <is>
-          <t>자연어 요구 (예: "SS Fan 샤프트의 길이 계산…")</t>
+          <t>UQ(tenant_id, macro_name, version)</t>
         </is>
       </c>
     </row>
@@ -38848,11 +38844,11 @@
         </is>
       </c>
       <c r="B1120" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1120" s="2" t="inlineStr">
         <is>
-          <t>macro_expr</t>
+          <t>prompt_text</t>
         </is>
       </c>
       <c r="D1120" s="2" t="inlineStr">
@@ -38869,7 +38865,7 @@
       <c r="G1120" s="2" t="inlineStr"/>
       <c r="H1120" s="2" t="inlineStr">
         <is>
-          <t>Excel 문법 계산식</t>
+          <t>자연어 요구 (예: "SS Fan 샤프트의 길이 계산…")</t>
         </is>
       </c>
     </row>
@@ -38880,16 +38876,16 @@
         </is>
       </c>
       <c r="B1121" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1121" s="2" t="inlineStr">
         <is>
-          <t>flowchart_def</t>
+          <t>macro_expr</t>
         </is>
       </c>
       <c r="D1121" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E1121" s="2" t="inlineStr">
@@ -38901,7 +38897,7 @@
       <c r="G1121" s="2" t="inlineStr"/>
       <c r="H1121" s="2" t="inlineStr">
         <is>
-          <t>Flowchart 그래프</t>
+          <t>Excel 문법 계산식</t>
         </is>
       </c>
     </row>
@@ -38912,16 +38908,16 @@
         </is>
       </c>
       <c r="B1122" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1122" s="2" t="inlineStr">
         <is>
-          <t>description_text</t>
+          <t>flowchart_def</t>
         </is>
       </c>
       <c r="D1122" s="2" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1122" s="2" t="inlineStr">
@@ -38933,7 +38929,7 @@
       <c r="G1122" s="2" t="inlineStr"/>
       <c r="H1122" s="2" t="inlineStr">
         <is>
-          <t>상세 설명</t>
+          <t>Flowchart 그래프</t>
         </is>
       </c>
     </row>
@@ -38944,11 +38940,11 @@
         </is>
       </c>
       <c r="B1123" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1123" s="2" t="inlineStr">
         <is>
-          <t>code_text</t>
+          <t>description_text</t>
         </is>
       </c>
       <c r="D1123" s="2" t="inlineStr">
@@ -38965,7 +38961,7 @@
       <c r="G1123" s="2" t="inlineStr"/>
       <c r="H1123" s="2" t="inlineStr">
         <is>
-          <t>AI 생성 Coding</t>
+          <t>상세 설명</t>
         </is>
       </c>
     </row>
@@ -38976,36 +38972,28 @@
         </is>
       </c>
       <c r="B1124" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1124" s="2" t="inlineStr">
         <is>
-          <t>apply_type</t>
+          <t>code_text</t>
         </is>
       </c>
       <c r="D1124" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E1124" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1124" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="G1124" s="2" t="inlineStr">
-        <is>
-          <t>'MACRO'::character varying</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1124" s="2" t="inlineStr"/>
+      <c r="G1124" s="2" t="inlineStr"/>
       <c r="H1124" s="2" t="inlineStr">
         <is>
-          <t>MACRO(간단) / CODING(복잡)</t>
+          <t>AI 생성 Coding</t>
         </is>
       </c>
     </row>
@@ -39016,28 +39004,36 @@
         </is>
       </c>
       <c r="B1125" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1125" s="2" t="inlineStr">
         <is>
-          <t>test_input</t>
+          <t>apply_type</t>
         </is>
       </c>
       <c r="D1125" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E1125" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1125" s="2" t="inlineStr"/>
-      <c r="G1125" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1125" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G1125" s="2" t="inlineStr">
+        <is>
+          <t>'MACRO'::character varying</t>
+        </is>
+      </c>
       <c r="H1125" s="2" t="inlineStr">
         <is>
-          <t>검증용 조건값</t>
+          <t>MACRO(간단) / CODING(복잡)</t>
         </is>
       </c>
     </row>
@@ -39048,11 +39044,11 @@
         </is>
       </c>
       <c r="B1126" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1126" s="2" t="inlineStr">
         <is>
-          <t>test_result</t>
+          <t>test_input</t>
         </is>
       </c>
       <c r="D1126" s="2" t="inlineStr">
@@ -39069,7 +39065,7 @@
       <c r="G1126" s="2" t="inlineStr"/>
       <c r="H1126" s="2" t="inlineStr">
         <is>
-          <t>Run 결과 (예: 786)</t>
+          <t>검증용 조건값</t>
         </is>
       </c>
     </row>
@@ -39080,36 +39076,28 @@
         </is>
       </c>
       <c r="B1127" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1127" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>test_result</t>
         </is>
       </c>
       <c r="D1127" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1127" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1127" s="2" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="G1127" s="2" t="inlineStr">
-        <is>
-          <t>'DRAFT'::character varying</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1127" s="2" t="inlineStr"/>
+      <c r="G1127" s="2" t="inlineStr"/>
       <c r="H1127" s="2" t="inlineStr">
         <is>
-          <t>DRAFT / TESTED / PENDING / APPROVED</t>
+          <t>Run 결과 (예: 786)</t>
         </is>
       </c>
     </row>
@@ -39120,28 +39108,36 @@
         </is>
       </c>
       <c r="B1128" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1128" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_address</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D1128" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1128" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1128" s="2" t="inlineStr"/>
-      <c r="G1128" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1128" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G1128" s="2" t="inlineStr">
+        <is>
+          <t>'DRAFT'::character varying</t>
+        </is>
+      </c>
       <c r="H1128" s="2" t="inlineStr">
         <is>
-          <t>자산 저장 위치</t>
+          <t>DRAFT / TESTED / PENDING / APPROVED</t>
         </is>
       </c>
     </row>
@@ -39152,30 +39148,30 @@
         </is>
       </c>
       <c r="B1129" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1129" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>hierarchy_address</t>
         </is>
       </c>
       <c r="D1129" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E1129" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1129" s="2" t="inlineStr"/>
-      <c r="G1129" s="2" t="inlineStr">
-        <is>
-          <t>'system'::character varying</t>
-        </is>
-      </c>
-      <c r="H1129" s="2" t="inlineStr"/>
+      <c r="G1129" s="2" t="inlineStr"/>
+      <c r="H1129" s="2" t="inlineStr">
+        <is>
+          <t>자산 저장 위치</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" s="2" t="inlineStr">
@@ -39184,16 +39180,16 @@
         </is>
       </c>
       <c r="B1130" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1130" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1130" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1130" s="2" t="inlineStr">
@@ -39204,7 +39200,7 @@
       <c r="F1130" s="2" t="inlineStr"/>
       <c r="G1130" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'system'::character varying</t>
         </is>
       </c>
       <c r="H1130" s="2" t="inlineStr"/>
@@ -39216,25 +39212,29 @@
         </is>
       </c>
       <c r="B1131" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1131" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1131" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1131" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1131" s="2" t="inlineStr"/>
-      <c r="G1131" s="2" t="inlineStr"/>
+      <c r="G1131" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1131" s="2" t="inlineStr"/>
     </row>
     <row r="1132">
@@ -39244,16 +39244,16 @@
         </is>
       </c>
       <c r="B1132" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1132" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D1132" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1132" s="2" t="inlineStr">
@@ -39272,16 +39272,16 @@
         </is>
       </c>
       <c r="B1133" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1133" s="2" t="inlineStr">
         <is>
-          <t>graph_def</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1133" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1133" s="2" t="inlineStr">
@@ -39300,16 +39300,16 @@
         </is>
       </c>
       <c r="B1134" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1134" s="2" t="inlineStr">
         <is>
-          <t>graph_checksum</t>
+          <t>graph_def</t>
         </is>
       </c>
       <c r="D1134" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1134" s="2" t="inlineStr">
@@ -39328,29 +39328,25 @@
         </is>
       </c>
       <c r="B1135" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1135" s="2" t="inlineStr">
         <is>
-          <t>view_fingerprints</t>
+          <t>graph_checksum</t>
         </is>
       </c>
       <c r="D1135" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E1135" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1135" s="2" t="inlineStr"/>
-      <c r="G1135" s="2" t="inlineStr">
-        <is>
-          <t>'{}'::jsonb</t>
-        </is>
-      </c>
+      <c r="G1135" s="2" t="inlineStr"/>
       <c r="H1135" s="2" t="inlineStr"/>
     </row>
     <row r="1136">
@@ -39360,56 +39356,56 @@
         </is>
       </c>
       <c r="B1136" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1136" s="2" t="inlineStr">
         <is>
-          <t>graph_synced_at</t>
+          <t>view_fingerprints</t>
         </is>
       </c>
       <c r="D1136" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1136" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1136" s="2" t="inlineStr"/>
-      <c r="G1136" s="2" t="inlineStr"/>
+      <c r="G1136" s="2" t="inlineStr">
+        <is>
+          <t>'{}'::jsonb</t>
+        </is>
+      </c>
       <c r="H1136" s="2" t="inlineStr"/>
     </row>
     <row r="1137">
       <c r="A1137" s="2" t="inlineStr">
         <is>
-          <t>tbx_macro_ref</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="B1137" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C1137" s="2" t="inlineStr">
         <is>
-          <t>ref_id</t>
+          <t>graph_synced_at</t>
         </is>
       </c>
       <c r="D1137" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1137" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1137" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1137" s="2" t="inlineStr"/>
       <c r="G1137" s="2" t="inlineStr"/>
       <c r="H1137" s="2" t="inlineStr"/>
     </row>
@@ -39420,11 +39416,11 @@
         </is>
       </c>
       <c r="B1138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1138" s="2" t="inlineStr">
         <is>
-          <t>macro_id</t>
+          <t>ref_id</t>
         </is>
       </c>
       <c r="D1138" s="2" t="inlineStr">
@@ -39439,7 +39435,7 @@
       </c>
       <c r="F1138" s="2" t="inlineStr">
         <is>
-          <t>FK→tbx_macro</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="G1138" s="2" t="inlineStr"/>
@@ -39452,16 +39448,16 @@
         </is>
       </c>
       <c r="B1139" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1139" s="2" t="inlineStr">
         <is>
-          <t>ref_type</t>
+          <t>macro_id</t>
         </is>
       </c>
       <c r="D1139" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1139" s="2" t="inlineStr">
@@ -39469,13 +39465,13 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1139" s="2" t="inlineStr"/>
+      <c r="F1139" s="2" t="inlineStr">
+        <is>
+          <t>FK→tbx_macro</t>
+        </is>
+      </c>
       <c r="G1139" s="2" t="inlineStr"/>
-      <c r="H1139" s="2" t="inlineStr">
-        <is>
-          <t>TABLE / VARIANT / MACRO / DIMENSION</t>
-        </is>
-      </c>
+      <c r="H1139" s="2" t="inlineStr"/>
     </row>
     <row r="1140">
       <c r="A1140" s="2" t="inlineStr">
@@ -39484,16 +39480,16 @@
         </is>
       </c>
       <c r="B1140" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1140" s="2" t="inlineStr">
         <is>
-          <t>ref_target_id</t>
+          <t>ref_type</t>
         </is>
       </c>
       <c r="D1140" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1140" s="2" t="inlineStr">
@@ -39505,22 +39501,22 @@
       <c r="G1140" s="2" t="inlineStr"/>
       <c r="H1140" s="2" t="inlineStr">
         <is>
-          <t>참조 대상 PK</t>
+          <t>TABLE / VARIANT / MACRO / DIMENSION</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" s="2" t="inlineStr">
         <is>
-          <t>tbx_package</t>
+          <t>tbx_macro_ref</t>
         </is>
       </c>
       <c r="B1141" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1141" s="2" t="inlineStr">
         <is>
-          <t>package_id</t>
+          <t>ref_target_id</t>
         </is>
       </c>
       <c r="D1141" s="2" t="inlineStr">
@@ -39533,17 +39529,13 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1141" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1141" s="2" t="inlineStr">
-        <is>
-          <t>nextval('tbx_package_package_id_seq'::regclass)</t>
-        </is>
-      </c>
-      <c r="H1141" s="2" t="inlineStr"/>
+      <c r="F1141" s="2" t="inlineStr"/>
+      <c r="G1141" s="2" t="inlineStr"/>
+      <c r="H1141" s="2" t="inlineStr">
+        <is>
+          <t>참조 대상 PK</t>
+        </is>
+      </c>
     </row>
     <row r="1142">
       <c r="A1142" s="2" t="inlineStr">
@@ -39552,11 +39544,11 @@
         </is>
       </c>
       <c r="B1142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1142" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>package_id</t>
         </is>
       </c>
       <c r="D1142" s="2" t="inlineStr">
@@ -39571,10 +39563,14 @@
       </c>
       <c r="F1142" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G1142" s="2" t="inlineStr"/>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G1142" s="2" t="inlineStr">
+        <is>
+          <t>nextval('tbx_package_package_id_seq'::regclass)</t>
+        </is>
+      </c>
       <c r="H1142" s="2" t="inlineStr"/>
     </row>
     <row r="1143">
@@ -39584,16 +39580,16 @@
         </is>
       </c>
       <c r="B1143" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1143" s="2" t="inlineStr">
         <is>
-          <t>package_code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1143" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(40)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1143" s="2" t="inlineStr">
@@ -39616,16 +39612,16 @@
         </is>
       </c>
       <c r="B1144" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1144" s="2" t="inlineStr">
         <is>
-          <t>package_name</t>
+          <t>package_code</t>
         </is>
       </c>
       <c r="D1144" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="E1144" s="2" t="inlineStr">
@@ -39633,7 +39629,11 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1144" s="2" t="inlineStr"/>
+      <c r="F1144" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G1144" s="2" t="inlineStr"/>
       <c r="H1144" s="2" t="inlineStr"/>
     </row>
@@ -39644,16 +39644,16 @@
         </is>
       </c>
       <c r="B1145" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1145" s="2" t="inlineStr">
         <is>
-          <t>version_no</t>
+          <t>package_name</t>
         </is>
       </c>
       <c r="D1145" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="E1145" s="2" t="inlineStr">
@@ -39661,16 +39661,8 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1145" s="2" t="inlineStr">
-        <is>
-          <t>UQ</t>
-        </is>
-      </c>
-      <c r="G1145" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F1145" s="2" t="inlineStr"/>
+      <c r="G1145" s="2" t="inlineStr"/>
       <c r="H1145" s="2" t="inlineStr"/>
     </row>
     <row r="1146">
@@ -39680,16 +39672,16 @@
         </is>
       </c>
       <c r="B1146" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1146" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>version_no</t>
         </is>
       </c>
       <c r="D1146" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(12)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="E1146" s="2" t="inlineStr">
@@ -39699,12 +39691,12 @@
       </c>
       <c r="F1146" s="2" t="inlineStr">
         <is>
-          <t>CHECK</t>
+          <t>UQ</t>
         </is>
       </c>
       <c r="G1146" s="2" t="inlineStr">
         <is>
-          <t>'DRAFT'::character varying</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H1146" s="2" t="inlineStr"/>
@@ -39716,16 +39708,16 @@
         </is>
       </c>
       <c r="B1147" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1147" s="2" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D1147" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(12)</t>
         </is>
       </c>
       <c r="E1147" s="2" t="inlineStr">
@@ -39740,7 +39732,7 @@
       </c>
       <c r="G1147" s="2" t="inlineStr">
         <is>
-          <t>'LOW'::character varying</t>
+          <t>'DRAFT'::character varying</t>
         </is>
       </c>
       <c r="H1147" s="2" t="inlineStr"/>
@@ -39752,25 +39744,33 @@
         </is>
       </c>
       <c r="B1148" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1148" s="2" t="inlineStr">
         <is>
-          <t>guard_report</t>
+          <t>risk_level</t>
         </is>
       </c>
       <c r="D1148" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E1148" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1148" s="2" t="inlineStr"/>
-      <c r="G1148" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1148" s="2" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="G1148" s="2" t="inlineStr">
+        <is>
+          <t>'LOW'::character varying</t>
+        </is>
+      </c>
       <c r="H1148" s="2" t="inlineStr"/>
     </row>
     <row r="1149">
@@ -39780,11 +39780,11 @@
         </is>
       </c>
       <c r="B1149" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1149" s="2" t="inlineStr">
         <is>
-          <t>sandbox_report</t>
+          <t>guard_report</t>
         </is>
       </c>
       <c r="D1149" s="2" t="inlineStr">
@@ -39808,16 +39808,16 @@
         </is>
       </c>
       <c r="B1150" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1150" s="2" t="inlineStr">
         <is>
-          <t>checksum</t>
+          <t>sandbox_report</t>
         </is>
       </c>
       <c r="D1150" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1150" s="2" t="inlineStr">
@@ -39836,16 +39836,16 @@
         </is>
       </c>
       <c r="B1151" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1151" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>checksum</t>
         </is>
       </c>
       <c r="D1151" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(300)</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E1151" s="2" t="inlineStr">
@@ -39864,29 +39864,25 @@
         </is>
       </c>
       <c r="B1152" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1152" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>note</t>
         </is>
       </c>
       <c r="D1152" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(300)</t>
         </is>
       </c>
       <c r="E1152" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1152" s="2" t="inlineStr"/>
-      <c r="G1152" s="2" t="inlineStr">
-        <is>
-          <t>'system'::character varying</t>
-        </is>
-      </c>
+      <c r="G1152" s="2" t="inlineStr"/>
       <c r="H1152" s="2" t="inlineStr"/>
     </row>
     <row r="1153">
@@ -39896,16 +39892,16 @@
         </is>
       </c>
       <c r="B1153" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1153" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1153" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1153" s="2" t="inlineStr">
@@ -39916,7 +39912,7 @@
       <c r="F1153" s="2" t="inlineStr"/>
       <c r="G1153" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'system'::character varying</t>
         </is>
       </c>
       <c r="H1153" s="2" t="inlineStr"/>
@@ -39928,25 +39924,29 @@
         </is>
       </c>
       <c r="B1154" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1154" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1154" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1154" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1154" s="2" t="inlineStr"/>
-      <c r="G1154" s="2" t="inlineStr"/>
+      <c r="G1154" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1154" s="2" t="inlineStr"/>
     </row>
     <row r="1155">
@@ -39956,16 +39956,16 @@
         </is>
       </c>
       <c r="B1155" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1155" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D1155" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1155" s="2" t="inlineStr">
@@ -39984,11 +39984,11 @@
         </is>
       </c>
       <c r="B1156" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1156" s="2" t="inlineStr">
         <is>
-          <t>published_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1156" s="2" t="inlineStr">
@@ -40012,29 +40012,25 @@
         </is>
       </c>
       <c r="B1157" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1157" s="2" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>published_at</t>
         </is>
       </c>
       <c r="D1157" s="2" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1157" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1157" s="2" t="inlineStr"/>
-      <c r="G1157" s="2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="G1157" s="2" t="inlineStr"/>
       <c r="H1157" s="2" t="inlineStr"/>
     </row>
     <row r="1158">
@@ -40044,61 +40040,57 @@
         </is>
       </c>
       <c r="B1158" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1158" s="2" t="inlineStr">
         <is>
-          <t>activated_at</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D1158" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="E1158" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1158" s="2" t="inlineStr"/>
-      <c r="G1158" s="2" t="inlineStr"/>
+      <c r="G1158" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="H1158" s="2" t="inlineStr"/>
     </row>
     <row r="1159">
       <c r="A1159" s="2" t="inlineStr">
         <is>
-          <t>tbx_package_item</t>
+          <t>tbx_package</t>
         </is>
       </c>
       <c r="B1159" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C1159" s="2" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>activated_at</t>
         </is>
       </c>
       <c r="D1159" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1159" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1159" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1159" s="2" t="inlineStr">
-        <is>
-          <t>nextval('tbx_package_item_item_id_seq'::regclass)</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1159" s="2" t="inlineStr"/>
+      <c r="G1159" s="2" t="inlineStr"/>
       <c r="H1159" s="2" t="inlineStr"/>
     </row>
     <row r="1160">
@@ -40108,11 +40100,11 @@
         </is>
       </c>
       <c r="B1160" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1160" s="2" t="inlineStr">
         <is>
-          <t>package_id</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="D1160" s="2" t="inlineStr">
@@ -40127,10 +40119,14 @@
       </c>
       <c r="F1160" s="2" t="inlineStr">
         <is>
-          <t>FK→tbx_package · UQ</t>
-        </is>
-      </c>
-      <c r="G1160" s="2" t="inlineStr"/>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G1160" s="2" t="inlineStr">
+        <is>
+          <t>nextval('tbx_package_item_item_id_seq'::regclass)</t>
+        </is>
+      </c>
       <c r="H1160" s="2" t="inlineStr"/>
     </row>
     <row r="1161">
@@ -40140,16 +40136,16 @@
         </is>
       </c>
       <c r="B1161" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1161" s="2" t="inlineStr">
         <is>
-          <t>item_type</t>
+          <t>package_id</t>
         </is>
       </c>
       <c r="D1161" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1161" s="2" t="inlineStr">
@@ -40159,7 +40155,7 @@
       </c>
       <c r="F1161" s="2" t="inlineStr">
         <is>
-          <t>CHECK · UQ</t>
+          <t>FK→tbx_package · UQ</t>
         </is>
       </c>
       <c r="G1161" s="2" t="inlineStr"/>
@@ -40172,16 +40168,16 @@
         </is>
       </c>
       <c r="B1162" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1162" s="2" t="inlineStr">
         <is>
-          <t>item_ref</t>
+          <t>item_type</t>
         </is>
       </c>
       <c r="D1162" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E1162" s="2" t="inlineStr">
@@ -40191,7 +40187,7 @@
       </c>
       <c r="F1162" s="2" t="inlineStr">
         <is>
-          <t>UQ</t>
+          <t>CHECK · UQ</t>
         </is>
       </c>
       <c r="G1162" s="2" t="inlineStr"/>
@@ -40204,56 +40200,56 @@
         </is>
       </c>
       <c r="B1163" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1163" s="2" t="inlineStr">
         <is>
-          <t>snapshot</t>
+          <t>item_ref</t>
         </is>
       </c>
       <c r="D1163" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="E1163" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F1163" s="2" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F1163" s="2" t="inlineStr">
+        <is>
+          <t>UQ</t>
+        </is>
+      </c>
       <c r="G1163" s="2" t="inlineStr"/>
       <c r="H1163" s="2" t="inlineStr"/>
     </row>
     <row r="1164">
       <c r="A1164" s="2" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>tbx_package_item</t>
         </is>
       </c>
       <c r="B1164" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1164" s="2" t="inlineStr">
         <is>
-          <t>templet_id</t>
+          <t>snapshot</t>
         </is>
       </c>
       <c r="D1164" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1164" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F1164" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1164" s="2" t="inlineStr"/>
       <c r="G1164" s="2" t="inlineStr"/>
       <c r="H1164" s="2" t="inlineStr"/>
     </row>
@@ -40264,11 +40260,11 @@
         </is>
       </c>
       <c r="B1165" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1165" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>templet_id</t>
         </is>
       </c>
       <c r="D1165" s="2" t="inlineStr">
@@ -40281,7 +40277,11 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1165" s="2" t="inlineStr"/>
+      <c r="F1165" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G1165" s="2" t="inlineStr"/>
       <c r="H1165" s="2" t="inlineStr"/>
     </row>
@@ -40292,16 +40292,16 @@
         </is>
       </c>
       <c r="B1166" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1166" s="2" t="inlineStr">
         <is>
-          <t>templet_name</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1166" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1166" s="2" t="inlineStr">
@@ -40320,16 +40320,16 @@
         </is>
       </c>
       <c r="B1167" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1167" s="2" t="inlineStr">
         <is>
-          <t>templet_type</t>
+          <t>templet_name</t>
         </is>
       </c>
       <c r="D1167" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E1167" s="2" t="inlineStr">
@@ -40339,11 +40339,7 @@
       </c>
       <c r="F1167" s="2" t="inlineStr"/>
       <c r="G1167" s="2" t="inlineStr"/>
-      <c r="H1167" s="2" t="inlineStr">
-        <is>
-          <t>COMMAND_BUTTON / COMBO_BOX / DATA_TABLE / PRINT_FORM / GRAPH / SCREEN</t>
-        </is>
-      </c>
+      <c r="H1167" s="2" t="inlineStr"/>
     </row>
     <row r="1168">
       <c r="A1168" s="2" t="inlineStr">
@@ -40352,16 +40348,16 @@
         </is>
       </c>
       <c r="B1168" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1168" s="2" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>templet_type</t>
         </is>
       </c>
       <c r="D1168" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="E1168" s="2" t="inlineStr">
@@ -40373,7 +40369,7 @@
       <c r="G1168" s="2" t="inlineStr"/>
       <c r="H1168" s="2" t="inlineStr">
         <is>
-          <t>동작(저장/삭제/복사/등록/찾기)·대상·Data 바인딩</t>
+          <t>COMMAND_BUTTON / COMBO_BOX / DATA_TABLE / PRINT_FORM / GRAPH / SCREEN</t>
         </is>
       </c>
     </row>
@@ -40384,16 +40380,16 @@
         </is>
       </c>
       <c r="B1169" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1169" s="2" t="inlineStr">
         <is>
-          <t>is_system</t>
+          <t>definition</t>
         </is>
       </c>
       <c r="D1169" s="2" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1169" s="2" t="inlineStr">
@@ -40402,12 +40398,12 @@
         </is>
       </c>
       <c r="F1169" s="2" t="inlineStr"/>
-      <c r="G1169" s="2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H1169" s="2" t="inlineStr"/>
+      <c r="G1169" s="2" t="inlineStr"/>
+      <c r="H1169" s="2" t="inlineStr">
+        <is>
+          <t>동작(저장/삭제/복사/등록/찾기)·대상·Data 바인딩</t>
+        </is>
+      </c>
     </row>
     <row r="1170">
       <c r="A1170" s="2" t="inlineStr">
@@ -40416,16 +40412,16 @@
         </is>
       </c>
       <c r="B1170" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1170" s="2" t="inlineStr">
         <is>
-          <t>approval_status</t>
+          <t>is_system</t>
         </is>
       </c>
       <c r="D1170" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="E1170" s="2" t="inlineStr">
@@ -40436,7 +40432,7 @@
       <c r="F1170" s="2" t="inlineStr"/>
       <c r="G1170" s="2" t="inlineStr">
         <is>
-          <t>'DRAFT'::character varying</t>
+          <t>false</t>
         </is>
       </c>
       <c r="H1170" s="2" t="inlineStr"/>
@@ -40448,16 +40444,16 @@
         </is>
       </c>
       <c r="B1171" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1171" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="D1171" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1171" s="2" t="inlineStr">
@@ -40468,7 +40464,7 @@
       <c r="F1171" s="2" t="inlineStr"/>
       <c r="G1171" s="2" t="inlineStr">
         <is>
-          <t>'system'::character varying</t>
+          <t>'DRAFT'::character varying</t>
         </is>
       </c>
       <c r="H1171" s="2" t="inlineStr"/>
@@ -40480,16 +40476,16 @@
         </is>
       </c>
       <c r="B1172" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1172" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1172" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1172" s="2" t="inlineStr">
@@ -40500,7 +40496,7 @@
       <c r="F1172" s="2" t="inlineStr"/>
       <c r="G1172" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'system'::character varying</t>
         </is>
       </c>
       <c r="H1172" s="2" t="inlineStr"/>
@@ -40512,25 +40508,29 @@
         </is>
       </c>
       <c r="B1173" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1173" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1173" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1173" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1173" s="2" t="inlineStr"/>
-      <c r="G1173" s="2" t="inlineStr"/>
+      <c r="G1173" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1173" s="2" t="inlineStr"/>
     </row>
     <row r="1174">
@@ -40540,16 +40540,16 @@
         </is>
       </c>
       <c r="B1174" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1174" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D1174" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1174" s="2" t="inlineStr">
@@ -40568,16 +40568,16 @@
         </is>
       </c>
       <c r="B1175" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1175" s="2" t="inlineStr">
         <is>
-          <t>origin_templet_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1175" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1175" s="2" t="inlineStr">
@@ -40596,48 +40596,44 @@
         </is>
       </c>
       <c r="B1176" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1176" s="2" t="inlineStr">
         <is>
-          <t>locked_fields</t>
+          <t>origin_templet_id</t>
         </is>
       </c>
       <c r="D1176" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1176" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1176" s="2" t="inlineStr"/>
-      <c r="G1176" s="2" t="inlineStr">
-        <is>
-          <t>'[]'::jsonb</t>
-        </is>
-      </c>
+      <c r="G1176" s="2" t="inlineStr"/>
       <c r="H1176" s="2" t="inlineStr"/>
     </row>
     <row r="1177">
       <c r="A1177" s="2" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="B1177" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1177" s="2" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>locked_fields</t>
         </is>
       </c>
       <c r="D1177" s="2" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1177" s="2" t="inlineStr">
@@ -40645,12 +40641,12 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1177" s="2" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G1177" s="2" t="inlineStr"/>
+      <c r="F1177" s="2" t="inlineStr"/>
+      <c r="G1177" s="2" t="inlineStr">
+        <is>
+          <t>'[]'::jsonb</t>
+        </is>
+      </c>
       <c r="H1177" s="2" t="inlineStr"/>
     </row>
     <row r="1178">
@@ -40660,11 +40656,11 @@
         </is>
       </c>
       <c r="B1178" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1178" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="D1178" s="2" t="inlineStr">
@@ -40677,7 +40673,11 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="F1178" s="2" t="inlineStr"/>
+      <c r="F1178" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="G1178" s="2" t="inlineStr"/>
       <c r="H1178" s="2" t="inlineStr"/>
     </row>
@@ -40688,16 +40688,16 @@
         </is>
       </c>
       <c r="B1179" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1179" s="2" t="inlineStr">
         <is>
-          <t>form_name</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1179" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E1179" s="2" t="inlineStr">
@@ -40716,16 +40716,16 @@
         </is>
       </c>
       <c r="B1180" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1180" s="2" t="inlineStr">
         <is>
-          <t>form_type</t>
+          <t>form_name</t>
         </is>
       </c>
       <c r="D1180" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E1180" s="2" t="inlineStr">
@@ -40735,11 +40735,7 @@
       </c>
       <c r="F1180" s="2" t="inlineStr"/>
       <c r="G1180" s="2" t="inlineStr"/>
-      <c r="H1180" s="2" t="inlineStr">
-        <is>
-          <t>CPQ_SELECTION / TECHNICAL / DOCUMENT / ERP / PRINT</t>
-        </is>
-      </c>
+      <c r="H1180" s="2" t="inlineStr"/>
     </row>
     <row r="1181">
       <c r="A1181" s="2" t="inlineStr">
@@ -40748,16 +40744,16 @@
         </is>
       </c>
       <c r="B1181" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1181" s="2" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>form_type</t>
         </is>
       </c>
       <c r="D1181" s="2" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="E1181" s="2" t="inlineStr">
@@ -40766,12 +40762,12 @@
         </is>
       </c>
       <c r="F1181" s="2" t="inlineStr"/>
-      <c r="G1181" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H1181" s="2" t="inlineStr"/>
+      <c r="G1181" s="2" t="inlineStr"/>
+      <c r="H1181" s="2" t="inlineStr">
+        <is>
+          <t>CPQ_SELECTION / TECHNICAL / DOCUMENT / ERP / PRINT</t>
+        </is>
+      </c>
     </row>
     <row r="1182">
       <c r="A1182" s="2" t="inlineStr">
@@ -40780,16 +40776,16 @@
         </is>
       </c>
       <c r="B1182" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1182" s="2" t="inlineStr">
         <is>
-          <t>layout_def</t>
+          <t>version</t>
         </is>
       </c>
       <c r="D1182" s="2" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="E1182" s="2" t="inlineStr">
@@ -40798,12 +40794,12 @@
         </is>
       </c>
       <c r="F1182" s="2" t="inlineStr"/>
-      <c r="G1182" s="2" t="inlineStr"/>
-      <c r="H1182" s="2" t="inlineStr">
-        <is>
-          <t>Widget 트리 (Button/Label/Entry/Canvas/Combo…) + 동작 바인딩</t>
-        </is>
-      </c>
+      <c r="G1182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H1182" s="2" t="inlineStr"/>
     </row>
     <row r="1183">
       <c r="A1183" s="2" t="inlineStr">
@@ -40812,28 +40808,28 @@
         </is>
       </c>
       <c r="B1183" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1183" s="2" t="inlineStr">
         <is>
-          <t>hierarchy_address</t>
+          <t>layout_def</t>
         </is>
       </c>
       <c r="D1183" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="E1183" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1183" s="2" t="inlineStr"/>
       <c r="G1183" s="2" t="inlineStr"/>
       <c r="H1183" s="2" t="inlineStr">
         <is>
-          <t>Head/Work Place 연결 위치</t>
+          <t>Widget 트리 (Button/Label/Entry/Canvas/Combo…) + 동작 바인딩</t>
         </is>
       </c>
     </row>
@@ -40844,16 +40840,16 @@
         </is>
       </c>
       <c r="B1184" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1184" s="2" t="inlineStr">
         <is>
-          <t>head_key</t>
+          <t>hierarchy_address</t>
         </is>
       </c>
       <c r="D1184" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E1184" s="2" t="inlineStr">
@@ -40865,7 +40861,7 @@
       <c r="G1184" s="2" t="inlineStr"/>
       <c r="H1184" s="2" t="inlineStr">
         <is>
-          <t>Head-Templet 연결 (v0.2, SYS-020)</t>
+          <t>Head/Work Place 연결 위치</t>
         </is>
       </c>
     </row>
@@ -40876,32 +40872,28 @@
         </is>
       </c>
       <c r="B1185" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1185" s="2" t="inlineStr">
         <is>
-          <t>is_system</t>
+          <t>head_key</t>
         </is>
       </c>
       <c r="D1185" s="2" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1185" s="2" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="F1185" s="2" t="inlineStr"/>
-      <c r="G1185" s="2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+      <c r="G1185" s="2" t="inlineStr"/>
       <c r="H1185" s="2" t="inlineStr">
         <is>
-          <t>EDIM 제공 Form 여부</t>
+          <t>Head-Templet 연결 (v0.2, SYS-020)</t>
         </is>
       </c>
     </row>
@@ -40912,16 +40904,16 @@
         </is>
       </c>
       <c r="B1186" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1186" s="2" t="inlineStr">
         <is>
-          <t>approval_status</t>
+          <t>is_system</t>
         </is>
       </c>
       <c r="D1186" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="E1186" s="2" t="inlineStr">
@@ -40932,10 +40924,14 @@
       <c r="F1186" s="2" t="inlineStr"/>
       <c r="G1186" s="2" t="inlineStr">
         <is>
-          <t>'DRAFT'::character varying</t>
-        </is>
-      </c>
-      <c r="H1186" s="2" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H1186" s="2" t="inlineStr">
+        <is>
+          <t>EDIM 제공 Form 여부</t>
+        </is>
+      </c>
     </row>
     <row r="1187">
       <c r="A1187" s="2" t="inlineStr">
@@ -40944,16 +40940,16 @@
         </is>
       </c>
       <c r="B1187" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1187" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="D1187" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E1187" s="2" t="inlineStr">
@@ -40964,7 +40960,7 @@
       <c r="F1187" s="2" t="inlineStr"/>
       <c r="G1187" s="2" t="inlineStr">
         <is>
-          <t>'system'::character varying</t>
+          <t>'DRAFT'::character varying</t>
         </is>
       </c>
       <c r="H1187" s="2" t="inlineStr"/>
@@ -40976,16 +40972,16 @@
         </is>
       </c>
       <c r="B1188" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1188" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1188" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1188" s="2" t="inlineStr">
@@ -40996,7 +40992,7 @@
       <c r="F1188" s="2" t="inlineStr"/>
       <c r="G1188" s="2" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>'system'::character varying</t>
         </is>
       </c>
       <c r="H1188" s="2" t="inlineStr"/>
@@ -41008,25 +41004,29 @@
         </is>
       </c>
       <c r="B1189" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1189" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1189" s="2" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="E1189" s="2" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="F1189" s="2" t="inlineStr"/>
-      <c r="G1189" s="2" t="inlineStr"/>
+      <c r="G1189" s="2" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="H1189" s="2" t="inlineStr"/>
     </row>
     <row r="1190">
@@ -41036,16 +41036,16 @@
         </is>
       </c>
       <c r="B1190" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1190" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D1190" s="2" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E1190" s="2" t="inlineStr">
@@ -41056,6 +41056,34 @@
       <c r="F1190" s="2" t="inlineStr"/>
       <c r="G1190" s="2" t="inlineStr"/>
       <c r="H1190" s="2" t="inlineStr"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2" t="inlineStr">
+        <is>
+          <t>tbx_ui_form</t>
+        </is>
+      </c>
+      <c r="B1191" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1191" s="2" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D1191" s="2" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="E1191" s="2" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F1191" s="2" t="inlineStr"/>
+      <c r="G1191" s="2" t="inlineStr"/>
+      <c r="H1191" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43222,7 +43250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1010"/>
+  <dimension ref="A1:D1011"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -62582,25 +62610,29 @@
     <row r="889">
       <c r="A889" s="2" t="inlineStr">
         <is>
-          <t>테이블</t>
+          <t>컬럼</t>
         </is>
       </c>
       <c r="B889" s="2" t="inlineStr">
         <is>
-          <t>sys_user_pref</t>
-        </is>
-      </c>
-      <c r="C889" s="2" t="inlineStr"/>
+          <t>sys_user</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>pw_changed_at</t>
+        </is>
+      </c>
       <c r="D889" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
+          <t>설계 MD 에 설명 없음</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="2" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>테이블</t>
         </is>
       </c>
       <c r="B890" s="2" t="inlineStr">
@@ -62608,14 +62640,10 @@
           <t>sys_user_pref</t>
         </is>
       </c>
-      <c r="C890" s="2" t="inlineStr">
-        <is>
-          <t>pref_id</t>
-        </is>
-      </c>
+      <c r="C890" s="2" t="inlineStr"/>
       <c r="D890" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음</t>
+          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
         </is>
       </c>
     </row>
@@ -62632,7 +62660,7 @@
       </c>
       <c r="C891" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>pref_id</t>
         </is>
       </c>
       <c r="D891" s="2" t="inlineStr">
@@ -62654,7 +62682,7 @@
       </c>
       <c r="C892" s="2" t="inlineStr">
         <is>
-          <t>login_id</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D892" s="2" t="inlineStr">
@@ -62676,7 +62704,7 @@
       </c>
       <c r="C893" s="2" t="inlineStr">
         <is>
-          <t>pref_key</t>
+          <t>login_id</t>
         </is>
       </c>
       <c r="D893" s="2" t="inlineStr">
@@ -62698,7 +62726,7 @@
       </c>
       <c r="C894" s="2" t="inlineStr">
         <is>
-          <t>pref_value</t>
+          <t>pref_key</t>
         </is>
       </c>
       <c r="D894" s="2" t="inlineStr">
@@ -62720,7 +62748,7 @@
       </c>
       <c r="C895" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>pref_value</t>
         </is>
       </c>
       <c r="D895" s="2" t="inlineStr">
@@ -62737,12 +62765,12 @@
       </c>
       <c r="B896" s="2" t="inlineStr">
         <is>
-          <t>sys_user_role</t>
+          <t>sys_user_pref</t>
         </is>
       </c>
       <c r="C896" s="2" t="inlineStr">
         <is>
-          <t>user_role_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D896" s="2" t="inlineStr">
@@ -62764,7 +62792,7 @@
       </c>
       <c r="C897" s="2" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>user_role_id</t>
         </is>
       </c>
       <c r="D897" s="2" t="inlineStr">
@@ -62786,7 +62814,7 @@
       </c>
       <c r="C898" s="2" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D898" s="2" t="inlineStr">
@@ -62798,25 +62826,29 @@
     <row r="899">
       <c r="A899" s="2" t="inlineStr">
         <is>
-          <t>테이블</t>
+          <t>컬럼</t>
         </is>
       </c>
       <c r="B899" s="2" t="inlineStr">
         <is>
-          <t>sys_work_lock</t>
-        </is>
-      </c>
-      <c r="C899" s="2" t="inlineStr"/>
+          <t>sys_user_role</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>role_id</t>
+        </is>
+      </c>
       <c r="D899" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
+          <t>설계 MD 에 설명 없음</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="2" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>테이블</t>
         </is>
       </c>
       <c r="B900" s="2" t="inlineStr">
@@ -62824,14 +62856,10 @@
           <t>sys_work_lock</t>
         </is>
       </c>
-      <c r="C900" s="2" t="inlineStr">
-        <is>
-          <t>lock_id</t>
-        </is>
-      </c>
+      <c r="C900" s="2" t="inlineStr"/>
       <c r="D900" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음</t>
+          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
         </is>
       </c>
     </row>
@@ -62848,7 +62876,7 @@
       </c>
       <c r="C901" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>lock_id</t>
         </is>
       </c>
       <c r="D901" s="2" t="inlineStr">
@@ -62870,7 +62898,7 @@
       </c>
       <c r="C902" s="2" t="inlineStr">
         <is>
-          <t>resource_kind</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D902" s="2" t="inlineStr">
@@ -62892,7 +62920,7 @@
       </c>
       <c r="C903" s="2" t="inlineStr">
         <is>
-          <t>resource_key</t>
+          <t>resource_kind</t>
         </is>
       </c>
       <c r="D903" s="2" t="inlineStr">
@@ -62914,7 +62942,7 @@
       </c>
       <c r="C904" s="2" t="inlineStr">
         <is>
-          <t>holder_id</t>
+          <t>resource_key</t>
         </is>
       </c>
       <c r="D904" s="2" t="inlineStr">
@@ -62936,7 +62964,7 @@
       </c>
       <c r="C905" s="2" t="inlineStr">
         <is>
-          <t>acquired_at</t>
+          <t>holder_id</t>
         </is>
       </c>
       <c r="D905" s="2" t="inlineStr">
@@ -62958,7 +62986,7 @@
       </c>
       <c r="C906" s="2" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>acquired_at</t>
         </is>
       </c>
       <c r="D906" s="2" t="inlineStr">
@@ -62980,7 +63008,7 @@
       </c>
       <c r="C907" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="D907" s="2" t="inlineStr">
@@ -62992,25 +63020,29 @@
     <row r="908">
       <c r="A908" s="2" t="inlineStr">
         <is>
-          <t>테이블</t>
+          <t>컬럼</t>
         </is>
       </c>
       <c r="B908" s="2" t="inlineStr">
         <is>
-          <t>tax_code</t>
-        </is>
-      </c>
-      <c r="C908" s="2" t="inlineStr"/>
+          <t>sys_work_lock</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
       <c r="D908" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
+          <t>설계 MD 에 설명 없음</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>테이블</t>
         </is>
       </c>
       <c r="B909" s="2" t="inlineStr">
@@ -63018,14 +63050,10 @@
           <t>tax_code</t>
         </is>
       </c>
-      <c r="C909" s="2" t="inlineStr">
-        <is>
-          <t>tax_id</t>
-        </is>
-      </c>
+      <c r="C909" s="2" t="inlineStr"/>
       <c r="D909" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음</t>
+          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
         </is>
       </c>
     </row>
@@ -63042,7 +63070,7 @@
       </c>
       <c r="C910" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>tax_id</t>
         </is>
       </c>
       <c r="D910" s="2" t="inlineStr">
@@ -63064,7 +63092,7 @@
       </c>
       <c r="C911" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D911" s="2" t="inlineStr">
@@ -63086,7 +63114,7 @@
       </c>
       <c r="C912" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>code</t>
         </is>
       </c>
       <c r="D912" s="2" t="inlineStr">
@@ -63108,7 +63136,7 @@
       </c>
       <c r="C913" s="2" t="inlineStr">
         <is>
-          <t>rate_pct</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D913" s="2" t="inlineStr">
@@ -63130,7 +63158,7 @@
       </c>
       <c r="C914" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>rate_pct</t>
         </is>
       </c>
       <c r="D914" s="2" t="inlineStr">
@@ -63147,12 +63175,12 @@
       </c>
       <c r="B915" s="2" t="inlineStr">
         <is>
-          <t>tbl_data_row</t>
+          <t>tax_code</t>
         </is>
       </c>
       <c r="C915" s="2" t="inlineStr">
         <is>
-          <t>row_id</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D915" s="2" t="inlineStr">
@@ -63174,7 +63202,7 @@
       </c>
       <c r="C916" s="2" t="inlineStr">
         <is>
-          <t>table_id</t>
+          <t>row_id</t>
         </is>
       </c>
       <c r="D916" s="2" t="inlineStr">
@@ -63196,7 +63224,7 @@
       </c>
       <c r="C917" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>table_id</t>
         </is>
       </c>
       <c r="D917" s="2" t="inlineStr">
@@ -63213,12 +63241,12 @@
       </c>
       <c r="B918" s="2" t="inlineStr">
         <is>
-          <t>tbl_data_table</t>
+          <t>tbl_data_row</t>
         </is>
       </c>
       <c r="C918" s="2" t="inlineStr">
         <is>
-          <t>table_id</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="D918" s="2" t="inlineStr">
@@ -63240,7 +63268,7 @@
       </c>
       <c r="C919" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>table_id</t>
         </is>
       </c>
       <c r="D919" s="2" t="inlineStr">
@@ -63262,7 +63290,7 @@
       </c>
       <c r="C920" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D920" s="2" t="inlineStr">
@@ -63284,7 +63312,7 @@
       </c>
       <c r="C921" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D921" s="2" t="inlineStr">
@@ -63306,7 +63334,7 @@
       </c>
       <c r="C922" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D922" s="2" t="inlineStr">
@@ -63328,7 +63356,7 @@
       </c>
       <c r="C923" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D923" s="2" t="inlineStr">
@@ -63350,7 +63378,7 @@
       </c>
       <c r="C924" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D924" s="2" t="inlineStr">
@@ -63362,25 +63390,29 @@
     <row r="925">
       <c r="A925" s="2" t="inlineStr">
         <is>
-          <t>테이블</t>
+          <t>컬럼</t>
         </is>
       </c>
       <c r="B925" s="2" t="inlineStr">
         <is>
-          <t>tbx_binding_contract</t>
-        </is>
-      </c>
-      <c r="C925" s="2" t="inlineStr"/>
+          <t>tbl_data_table</t>
+        </is>
+      </c>
+      <c r="C925" s="2" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
       <c r="D925" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
+          <t>설계 MD 에 설명 없음</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>테이블</t>
         </is>
       </c>
       <c r="B926" s="2" t="inlineStr">
@@ -63388,14 +63420,10 @@
           <t>tbx_binding_contract</t>
         </is>
       </c>
-      <c r="C926" s="2" t="inlineStr">
-        <is>
-          <t>contract_id</t>
-        </is>
-      </c>
+      <c r="C926" s="2" t="inlineStr"/>
       <c r="D926" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음</t>
+          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
         </is>
       </c>
     </row>
@@ -63412,7 +63440,7 @@
       </c>
       <c r="C927" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>contract_id</t>
         </is>
       </c>
       <c r="D927" s="2" t="inlineStr">
@@ -63434,7 +63462,7 @@
       </c>
       <c r="C928" s="2" t="inlineStr">
         <is>
-          <t>contract_code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D928" s="2" t="inlineStr">
@@ -63456,7 +63484,7 @@
       </c>
       <c r="C929" s="2" t="inlineStr">
         <is>
-          <t>contract_name</t>
+          <t>contract_code</t>
         </is>
       </c>
       <c r="D929" s="2" t="inlineStr">
@@ -63478,7 +63506,7 @@
       </c>
       <c r="C930" s="2" t="inlineStr">
         <is>
-          <t>source_kind</t>
+          <t>contract_name</t>
         </is>
       </c>
       <c r="D930" s="2" t="inlineStr">
@@ -63500,7 +63528,7 @@
       </c>
       <c r="C931" s="2" t="inlineStr">
         <is>
-          <t>source_ref</t>
+          <t>source_kind</t>
         </is>
       </c>
       <c r="D931" s="2" t="inlineStr">
@@ -63522,7 +63550,7 @@
       </c>
       <c r="C932" s="2" t="inlineStr">
         <is>
-          <t>allowed_fields</t>
+          <t>source_ref</t>
         </is>
       </c>
       <c r="D932" s="2" t="inlineStr">
@@ -63544,7 +63572,7 @@
       </c>
       <c r="C933" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>allowed_fields</t>
         </is>
       </c>
       <c r="D933" s="2" t="inlineStr">
@@ -63566,7 +63594,7 @@
       </c>
       <c r="C934" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D934" s="2" t="inlineStr">
@@ -63588,7 +63616,7 @@
       </c>
       <c r="C935" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>note</t>
         </is>
       </c>
       <c r="D935" s="2" t="inlineStr">
@@ -63610,7 +63638,7 @@
       </c>
       <c r="C936" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D936" s="2" t="inlineStr">
@@ -63632,7 +63660,7 @@
       </c>
       <c r="C937" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D937" s="2" t="inlineStr">
@@ -63654,7 +63682,7 @@
       </c>
       <c r="C938" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D938" s="2" t="inlineStr">
@@ -63666,25 +63694,29 @@
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
         <is>
-          <t>테이블</t>
+          <t>컬럼</t>
         </is>
       </c>
       <c r="B939" s="2" t="inlineStr">
         <is>
-          <t>tbx_command</t>
-        </is>
-      </c>
-      <c r="C939" s="2" t="inlineStr"/>
+          <t>tbx_binding_contract</t>
+        </is>
+      </c>
+      <c r="C939" s="2" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
       <c r="D939" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
+          <t>설계 MD 에 설명 없음</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" s="2" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>테이블</t>
         </is>
       </c>
       <c r="B940" s="2" t="inlineStr">
@@ -63692,14 +63724,10 @@
           <t>tbx_command</t>
         </is>
       </c>
-      <c r="C940" s="2" t="inlineStr">
-        <is>
-          <t>command_id</t>
-        </is>
-      </c>
+      <c r="C940" s="2" t="inlineStr"/>
       <c r="D940" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음</t>
+          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
         </is>
       </c>
     </row>
@@ -63716,7 +63744,7 @@
       </c>
       <c r="C941" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>command_id</t>
         </is>
       </c>
       <c r="D941" s="2" t="inlineStr">
@@ -63738,7 +63766,7 @@
       </c>
       <c r="C942" s="2" t="inlineStr">
         <is>
-          <t>command_code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D942" s="2" t="inlineStr">
@@ -63760,7 +63788,7 @@
       </c>
       <c r="C943" s="2" t="inlineStr">
         <is>
-          <t>command_name</t>
+          <t>command_code</t>
         </is>
       </c>
       <c r="D943" s="2" t="inlineStr">
@@ -63782,7 +63810,7 @@
       </c>
       <c r="C944" s="2" t="inlineStr">
         <is>
-          <t>handler_kind</t>
+          <t>command_name</t>
         </is>
       </c>
       <c r="D944" s="2" t="inlineStr">
@@ -63804,7 +63832,7 @@
       </c>
       <c r="C945" s="2" t="inlineStr">
         <is>
-          <t>handler_ref</t>
+          <t>handler_kind</t>
         </is>
       </c>
       <c r="D945" s="2" t="inlineStr">
@@ -63826,7 +63854,7 @@
       </c>
       <c r="C946" s="2" t="inlineStr">
         <is>
-          <t>required_context</t>
+          <t>handler_ref</t>
         </is>
       </c>
       <c r="D946" s="2" t="inlineStr">
@@ -63848,7 +63876,7 @@
       </c>
       <c r="C947" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>required_context</t>
         </is>
       </c>
       <c r="D947" s="2" t="inlineStr">
@@ -63870,7 +63898,7 @@
       </c>
       <c r="C948" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D948" s="2" t="inlineStr">
@@ -63892,7 +63920,7 @@
       </c>
       <c r="C949" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>note</t>
         </is>
       </c>
       <c r="D949" s="2" t="inlineStr">
@@ -63914,7 +63942,7 @@
       </c>
       <c r="C950" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D950" s="2" t="inlineStr">
@@ -63936,7 +63964,7 @@
       </c>
       <c r="C951" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D951" s="2" t="inlineStr">
@@ -63958,7 +63986,7 @@
       </c>
       <c r="C952" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D952" s="2" t="inlineStr">
@@ -63975,12 +64003,12 @@
       </c>
       <c r="B953" s="2" t="inlineStr">
         <is>
-          <t>tbx_macro</t>
+          <t>tbx_command</t>
         </is>
       </c>
       <c r="C953" s="2" t="inlineStr">
         <is>
-          <t>macro_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D953" s="2" t="inlineStr">
@@ -64002,7 +64030,7 @@
       </c>
       <c r="C954" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>macro_id</t>
         </is>
       </c>
       <c r="D954" s="2" t="inlineStr">
@@ -64024,7 +64052,7 @@
       </c>
       <c r="C955" s="2" t="inlineStr">
         <is>
-          <t>macro_name</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D955" s="2" t="inlineStr">
@@ -64046,7 +64074,7 @@
       </c>
       <c r="C956" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>macro_name</t>
         </is>
       </c>
       <c r="D956" s="2" t="inlineStr">
@@ -64068,7 +64096,7 @@
       </c>
       <c r="C957" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D957" s="2" t="inlineStr">
@@ -64090,7 +64118,7 @@
       </c>
       <c r="C958" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D958" s="2" t="inlineStr">
@@ -64112,7 +64140,7 @@
       </c>
       <c r="C959" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D959" s="2" t="inlineStr">
@@ -64134,7 +64162,7 @@
       </c>
       <c r="C960" s="2" t="inlineStr">
         <is>
-          <t>graph_def</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D960" s="2" t="inlineStr">
@@ -64156,7 +64184,7 @@
       </c>
       <c r="C961" s="2" t="inlineStr">
         <is>
-          <t>graph_checksum</t>
+          <t>graph_def</t>
         </is>
       </c>
       <c r="D961" s="2" t="inlineStr">
@@ -64178,7 +64206,7 @@
       </c>
       <c r="C962" s="2" t="inlineStr">
         <is>
-          <t>view_fingerprints</t>
+          <t>graph_checksum</t>
         </is>
       </c>
       <c r="D962" s="2" t="inlineStr">
@@ -64200,7 +64228,7 @@
       </c>
       <c r="C963" s="2" t="inlineStr">
         <is>
-          <t>graph_synced_at</t>
+          <t>view_fingerprints</t>
         </is>
       </c>
       <c r="D963" s="2" t="inlineStr">
@@ -64217,12 +64245,12 @@
       </c>
       <c r="B964" s="2" t="inlineStr">
         <is>
-          <t>tbx_macro_ref</t>
+          <t>tbx_macro</t>
         </is>
       </c>
       <c r="C964" s="2" t="inlineStr">
         <is>
-          <t>ref_id</t>
+          <t>graph_synced_at</t>
         </is>
       </c>
       <c r="D964" s="2" t="inlineStr">
@@ -64244,7 +64272,7 @@
       </c>
       <c r="C965" s="2" t="inlineStr">
         <is>
-          <t>macro_id</t>
+          <t>ref_id</t>
         </is>
       </c>
       <c r="D965" s="2" t="inlineStr">
@@ -64256,25 +64284,29 @@
     <row r="966">
       <c r="A966" s="2" t="inlineStr">
         <is>
-          <t>테이블</t>
+          <t>컬럼</t>
         </is>
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>tbx_package</t>
-        </is>
-      </c>
-      <c r="C966" s="2" t="inlineStr"/>
+          <t>tbx_macro_ref</t>
+        </is>
+      </c>
+      <c r="C966" s="2" t="inlineStr">
+        <is>
+          <t>macro_id</t>
+        </is>
+      </c>
       <c r="D966" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
+          <t>설계 MD 에 설명 없음</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" s="2" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>테이블</t>
         </is>
       </c>
       <c r="B967" s="2" t="inlineStr">
@@ -64282,14 +64314,10 @@
           <t>tbx_package</t>
         </is>
       </c>
-      <c r="C967" s="2" t="inlineStr">
-        <is>
-          <t>package_id</t>
-        </is>
-      </c>
+      <c r="C967" s="2" t="inlineStr"/>
       <c r="D967" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음</t>
+          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
         </is>
       </c>
     </row>
@@ -64306,7 +64334,7 @@
       </c>
       <c r="C968" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>package_id</t>
         </is>
       </c>
       <c r="D968" s="2" t="inlineStr">
@@ -64328,7 +64356,7 @@
       </c>
       <c r="C969" s="2" t="inlineStr">
         <is>
-          <t>package_code</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D969" s="2" t="inlineStr">
@@ -64350,7 +64378,7 @@
       </c>
       <c r="C970" s="2" t="inlineStr">
         <is>
-          <t>package_name</t>
+          <t>package_code</t>
         </is>
       </c>
       <c r="D970" s="2" t="inlineStr">
@@ -64372,7 +64400,7 @@
       </c>
       <c r="C971" s="2" t="inlineStr">
         <is>
-          <t>version_no</t>
+          <t>package_name</t>
         </is>
       </c>
       <c r="D971" s="2" t="inlineStr">
@@ -64394,7 +64422,7 @@
       </c>
       <c r="C972" s="2" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>version_no</t>
         </is>
       </c>
       <c r="D972" s="2" t="inlineStr">
@@ -64416,7 +64444,7 @@
       </c>
       <c r="C973" s="2" t="inlineStr">
         <is>
-          <t>risk_level</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D973" s="2" t="inlineStr">
@@ -64438,7 +64466,7 @@
       </c>
       <c r="C974" s="2" t="inlineStr">
         <is>
-          <t>guard_report</t>
+          <t>risk_level</t>
         </is>
       </c>
       <c r="D974" s="2" t="inlineStr">
@@ -64460,7 +64488,7 @@
       </c>
       <c r="C975" s="2" t="inlineStr">
         <is>
-          <t>sandbox_report</t>
+          <t>guard_report</t>
         </is>
       </c>
       <c r="D975" s="2" t="inlineStr">
@@ -64482,7 +64510,7 @@
       </c>
       <c r="C976" s="2" t="inlineStr">
         <is>
-          <t>checksum</t>
+          <t>sandbox_report</t>
         </is>
       </c>
       <c r="D976" s="2" t="inlineStr">
@@ -64504,7 +64532,7 @@
       </c>
       <c r="C977" s="2" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>checksum</t>
         </is>
       </c>
       <c r="D977" s="2" t="inlineStr">
@@ -64526,7 +64554,7 @@
       </c>
       <c r="C978" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>note</t>
         </is>
       </c>
       <c r="D978" s="2" t="inlineStr">
@@ -64548,7 +64576,7 @@
       </c>
       <c r="C979" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D979" s="2" t="inlineStr">
@@ -64570,7 +64598,7 @@
       </c>
       <c r="C980" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D980" s="2" t="inlineStr">
@@ -64592,7 +64620,7 @@
       </c>
       <c r="C981" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D981" s="2" t="inlineStr">
@@ -64614,7 +64642,7 @@
       </c>
       <c r="C982" s="2" t="inlineStr">
         <is>
-          <t>published_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D982" s="2" t="inlineStr">
@@ -64636,7 +64664,7 @@
       </c>
       <c r="C983" s="2" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>published_at</t>
         </is>
       </c>
       <c r="D983" s="2" t="inlineStr">
@@ -64658,7 +64686,7 @@
       </c>
       <c r="C984" s="2" t="inlineStr">
         <is>
-          <t>activated_at</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D984" s="2" t="inlineStr">
@@ -64670,25 +64698,29 @@
     <row r="985">
       <c r="A985" s="2" t="inlineStr">
         <is>
-          <t>테이블</t>
+          <t>컬럼</t>
         </is>
       </c>
       <c r="B985" s="2" t="inlineStr">
         <is>
-          <t>tbx_package_item</t>
-        </is>
-      </c>
-      <c r="C985" s="2" t="inlineStr"/>
+          <t>tbx_package</t>
+        </is>
+      </c>
+      <c r="C985" s="2" t="inlineStr">
+        <is>
+          <t>activated_at</t>
+        </is>
+      </c>
       <c r="D985" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
+          <t>설계 MD 에 설명 없음</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" s="2" t="inlineStr">
         <is>
-          <t>컬럼</t>
+          <t>테이블</t>
         </is>
       </c>
       <c r="B986" s="2" t="inlineStr">
@@ -64696,14 +64728,10 @@
           <t>tbx_package_item</t>
         </is>
       </c>
-      <c r="C986" s="2" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
+      <c r="C986" s="2" t="inlineStr"/>
       <c r="D986" s="2" t="inlineStr">
         <is>
-          <t>설계 MD 에 설명 없음</t>
+          <t>설계 MD 에 설명 없음(alembic 로 추가된 테이블 등)</t>
         </is>
       </c>
     </row>
@@ -64720,7 +64748,7 @@
       </c>
       <c r="C987" s="2" t="inlineStr">
         <is>
-          <t>package_id</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="D987" s="2" t="inlineStr">
@@ -64742,7 +64770,7 @@
       </c>
       <c r="C988" s="2" t="inlineStr">
         <is>
-          <t>item_type</t>
+          <t>package_id</t>
         </is>
       </c>
       <c r="D988" s="2" t="inlineStr">
@@ -64764,7 +64792,7 @@
       </c>
       <c r="C989" s="2" t="inlineStr">
         <is>
-          <t>item_ref</t>
+          <t>item_type</t>
         </is>
       </c>
       <c r="D989" s="2" t="inlineStr">
@@ -64786,7 +64814,7 @@
       </c>
       <c r="C990" s="2" t="inlineStr">
         <is>
-          <t>snapshot</t>
+          <t>item_ref</t>
         </is>
       </c>
       <c r="D990" s="2" t="inlineStr">
@@ -64803,12 +64831,12 @@
       </c>
       <c r="B991" s="2" t="inlineStr">
         <is>
-          <t>tbx_templet</t>
+          <t>tbx_package_item</t>
         </is>
       </c>
       <c r="C991" s="2" t="inlineStr">
         <is>
-          <t>templet_id</t>
+          <t>snapshot</t>
         </is>
       </c>
       <c r="D991" s="2" t="inlineStr">
@@ -64830,7 +64858,7 @@
       </c>
       <c r="C992" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>templet_id</t>
         </is>
       </c>
       <c r="D992" s="2" t="inlineStr">
@@ -64852,7 +64880,7 @@
       </c>
       <c r="C993" s="2" t="inlineStr">
         <is>
-          <t>templet_name</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D993" s="2" t="inlineStr">
@@ -64874,7 +64902,7 @@
       </c>
       <c r="C994" s="2" t="inlineStr">
         <is>
-          <t>is_system</t>
+          <t>templet_name</t>
         </is>
       </c>
       <c r="D994" s="2" t="inlineStr">
@@ -64896,7 +64924,7 @@
       </c>
       <c r="C995" s="2" t="inlineStr">
         <is>
-          <t>approval_status</t>
+          <t>is_system</t>
         </is>
       </c>
       <c r="D995" s="2" t="inlineStr">
@@ -64918,7 +64946,7 @@
       </c>
       <c r="C996" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="D996" s="2" t="inlineStr">
@@ -64940,7 +64968,7 @@
       </c>
       <c r="C997" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D997" s="2" t="inlineStr">
@@ -64962,7 +64990,7 @@
       </c>
       <c r="C998" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D998" s="2" t="inlineStr">
@@ -64984,7 +65012,7 @@
       </c>
       <c r="C999" s="2" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="D999" s="2" t="inlineStr">
@@ -65006,7 +65034,7 @@
       </c>
       <c r="C1000" s="2" t="inlineStr">
         <is>
-          <t>origin_templet_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D1000" s="2" t="inlineStr">
@@ -65028,7 +65056,7 @@
       </c>
       <c r="C1001" s="2" t="inlineStr">
         <is>
-          <t>locked_fields</t>
+          <t>origin_templet_id</t>
         </is>
       </c>
       <c r="D1001" s="2" t="inlineStr">
@@ -65045,12 +65073,12 @@
       </c>
       <c r="B1002" s="2" t="inlineStr">
         <is>
-          <t>tbx_ui_form</t>
+          <t>tbx_templet</t>
         </is>
       </c>
       <c r="C1002" s="2" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>locked_fields</t>
         </is>
       </c>
       <c r="D1002" s="2" t="inlineStr">
@@ -65072,7 +65100,7 @@
       </c>
       <c r="C1003" s="2" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="D1003" s="2" t="inlineStr">
@@ -65094,7 +65122,7 @@
       </c>
       <c r="C1004" s="2" t="inlineStr">
         <is>
-          <t>form_name</t>
+          <t>tenant_id</t>
         </is>
       </c>
       <c r="D1004" s="2" t="inlineStr">
@@ -65116,7 +65144,7 @@
       </c>
       <c r="C1005" s="2" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>form_name</t>
         </is>
       </c>
       <c r="D1005" s="2" t="inlineStr">
@@ -65138,7 +65166,7 @@
       </c>
       <c r="C1006" s="2" t="inlineStr">
         <is>
-          <t>approval_status</t>
+          <t>version</t>
         </is>
       </c>
       <c r="D1006" s="2" t="inlineStr">
@@ -65160,7 +65188,7 @@
       </c>
       <c r="C1007" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="D1007" s="2" t="inlineStr">
@@ -65182,7 +65210,7 @@
       </c>
       <c r="C1008" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="D1008" s="2" t="inlineStr">
@@ -65204,7 +65232,7 @@
       </c>
       <c r="C1009" s="2" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D1009" s="2" t="inlineStr">
@@ -65226,10 +65254,32 @@
       </c>
       <c r="C1010" s="2" t="inlineStr">
         <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="D1010" s="2" t="inlineStr">
+        <is>
+          <t>설계 MD 에 설명 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="inlineStr">
+        <is>
+          <t>컬럼</t>
+        </is>
+      </c>
+      <c r="B1011" s="2" t="inlineStr">
+        <is>
+          <t>tbx_ui_form</t>
+        </is>
+      </c>
+      <c r="C1011" s="2" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D1010" s="2" t="inlineStr">
+      <c r="D1011" s="2" t="inlineStr">
         <is>
           <t>설계 MD 에 설명 없음</t>
         </is>
